--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8418E49A-8883-4B91-A567-F58F6C3DC79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC01701-9842-4073-8D53-FAA1F94300C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="exiobase" sheetId="1" r:id="rId1"/>
-    <sheet name="german" sheetId="2" r:id="rId2"/>
-    <sheet name="english" sheetId="4" r:id="rId3"/>
+    <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
+    <sheet name="Deutsch" sheetId="2" r:id="rId2"/>
+    <sheet name="English" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC01701-9842-4073-8D53-FAA1F94300C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C191DE7F-AEFB-45F0-BD04-25D70200450E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="296">
   <si>
     <t>impact</t>
   </si>
@@ -904,6 +904,12 @@
   </si>
   <si>
     <t>Landnutzung</t>
+  </si>
+  <si>
+    <t>Fälle</t>
+  </si>
+  <si>
+    <t>Kilotonnen</t>
   </si>
 </sst>
 </file>
@@ -3560,7 +3566,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -3917,7 +3923,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">

--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C191DE7F-AEFB-45F0-BD04-25D70200450E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD963403-C09E-4E77-A450-FC73F4810A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="297">
   <si>
     <t>impact</t>
   </si>
@@ -910,6 +910,9 @@
   </si>
   <si>
     <t>Kilotonnen</t>
+  </si>
+  <si>
+    <t>Mio. ha</t>
   </si>
 </sst>
 </file>
@@ -3492,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="D2" s="2">
         <v>2</v>
@@ -5617,17 +5620,18 @@
         <v>163</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D127" s="2">
         <v>2</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>163</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD963403-C09E-4E77-A450-FC73F4810A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C4A57A-57B4-4008-A375-E1593F02C062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="299">
   <si>
     <t>impact</t>
   </si>
@@ -534,21 +534,12 @@
     <t>Wertschöpfung</t>
   </si>
   <si>
-    <t>Milliarden Euro</t>
-  </si>
-  <si>
     <t>Beschäftigung</t>
   </si>
   <si>
-    <t>Millionen Personen</t>
-  </si>
-  <si>
     <t>Arbeitszeit</t>
   </si>
   <si>
-    <t>Millionen Stunden</t>
-  </si>
-  <si>
     <t>Treibhausgasemissionen</t>
   </si>
   <si>
@@ -642,9 +633,6 @@
     <t>Wasserverbrauch</t>
   </si>
   <si>
-    <t>Mm3 Wasser</t>
-  </si>
-  <si>
     <t>Blaue Wasserentnahme - Industrie</t>
   </si>
   <si>
@@ -912,7 +900,25 @@
     <t>Kilotonnen</t>
   </si>
   <si>
-    <t>Mio. ha</t>
+    <t>Mio. Personen</t>
+  </si>
+  <si>
+    <t>Mrd. Euro</t>
+  </si>
+  <si>
+    <t>Mio. Stunden</t>
+  </si>
+  <si>
+    <t>Mio. m³ Wasser</t>
+  </si>
+  <si>
+    <t>Mio. Hektar</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>Megatonnen</t>
   </si>
 </sst>
 </file>
@@ -3501,12 +3507,12 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>170</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -3518,12 +3524,12 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>172</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -3535,12 +3541,12 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>174</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -3552,12 +3558,12 @@
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -3569,12 +3575,12 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -3591,7 +3597,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -3608,7 +3614,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>20</v>
@@ -3625,7 +3631,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -3642,7 +3648,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
@@ -3659,7 +3665,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
@@ -3676,7 +3682,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -3693,7 +3699,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
@@ -3710,7 +3716,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
@@ -3727,7 +3733,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
@@ -3744,7 +3750,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>20</v>
@@ -3761,7 +3767,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>20</v>
@@ -3778,7 +3784,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>25</v>
@@ -3795,7 +3801,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>25</v>
@@ -3812,7 +3818,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>20</v>
@@ -3829,7 +3835,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
@@ -3846,7 +3852,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>20</v>
@@ -3863,7 +3869,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -3880,7 +3886,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>25</v>
@@ -3897,7 +3903,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>25</v>
@@ -3914,7 +3920,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
@@ -3926,12 +3932,12 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>42</v>
@@ -3943,12 +3949,12 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
@@ -3960,12 +3966,12 @@
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
@@ -3977,12 +3983,12 @@
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
@@ -3994,12 +4000,12 @@
         <v>2</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
@@ -4011,12 +4017,12 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
@@ -4028,12 +4034,12 @@
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
@@ -4045,12 +4051,12 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>206</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
@@ -4062,12 +4068,12 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
@@ -4079,12 +4085,12 @@
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
@@ -4096,12 +4102,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
@@ -4113,12 +4119,12 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>54</v>
@@ -4135,7 +4141,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>54</v>
@@ -4152,7 +4158,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>54</v>
@@ -4169,7 +4175,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>58</v>
@@ -4186,7 +4192,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>58</v>
@@ -4203,7 +4209,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>58</v>
@@ -4220,7 +4226,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>54</v>
@@ -4237,7 +4243,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>54</v>
@@ -4254,92 +4260,92 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D47" s="2">
         <v>2</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D48" s="2">
         <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D49" s="2">
         <v>2</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D50" s="2">
         <v>2</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D51" s="2">
         <v>2</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>69</v>
@@ -4356,7 +4362,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>71</v>
@@ -4373,7 +4379,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>71</v>
@@ -4390,7 +4396,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>71</v>
@@ -4407,7 +4413,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>71</v>
@@ -4424,7 +4430,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>71</v>
@@ -4441,7 +4447,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>71</v>
@@ -4458,7 +4464,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>71</v>
@@ -4475,7 +4481,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>71</v>
@@ -4492,7 +4498,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>71</v>
@@ -4509,7 +4515,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>71</v>
@@ -4526,7 +4532,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>71</v>
@@ -4543,7 +4549,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>71</v>
@@ -4560,7 +4566,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>71</v>
@@ -4577,7 +4583,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>71</v>
@@ -4594,7 +4600,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>71</v>
@@ -4611,7 +4617,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>71</v>
@@ -4628,7 +4634,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>71</v>
@@ -4645,7 +4651,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>71</v>
@@ -4662,7 +4668,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>71</v>
@@ -4679,7 +4685,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>71</v>
@@ -4696,7 +4702,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>71</v>
@@ -4713,7 +4719,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>71</v>
@@ -4730,7 +4736,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>71</v>
@@ -4747,7 +4753,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>71</v>
@@ -4764,7 +4770,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>96</v>
@@ -4781,7 +4787,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>96</v>
@@ -4798,7 +4804,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>99</v>
@@ -4815,7 +4821,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>99</v>
@@ -4832,7 +4838,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -4849,7 +4855,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>103</v>
@@ -4866,7 +4872,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -4883,7 +4889,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>106</v>
@@ -4900,7 +4906,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>108</v>
@@ -4917,7 +4923,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>110</v>
@@ -4929,12 +4935,12 @@
         <v>2</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>110</v>
+        <v>297</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>112</v>
@@ -4951,7 +4957,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>20</v>
@@ -4968,7 +4974,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
@@ -4985,7 +4991,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
@@ -5002,7 +5008,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
@@ -5019,7 +5025,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>20</v>
@@ -5036,7 +5042,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>20</v>
@@ -5053,7 +5059,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>123</v>
@@ -5070,7 +5076,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>20</v>
@@ -5087,7 +5093,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>126</v>
@@ -5104,7 +5110,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>20</v>
@@ -5121,7 +5127,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>129</v>
@@ -5138,7 +5144,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>115</v>
@@ -5155,7 +5161,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>129</v>
@@ -5172,7 +5178,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>133</v>
@@ -5189,7 +5195,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>135</v>
@@ -5206,7 +5212,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>137</v>
@@ -5223,53 +5229,53 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D104" s="2">
         <v>2</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>12</v>
+        <v>173</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C105" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D105" s="2">
         <v>2</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -5280,13 +5286,13 @@
         <v>140</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -5297,13 +5303,13 @@
         <v>140</v>
       </c>
       <c r="C108" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5314,13 +5320,13 @@
         <v>140</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -5331,18 +5337,18 @@
         <v>140</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>1000000000</v>
       </c>
       <c r="D110" s="2">
         <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>140</v>
+        <v>298</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>40</v>
@@ -5359,7 +5365,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>40</v>
@@ -5376,7 +5382,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>40</v>
@@ -5410,7 +5416,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>40</v>
@@ -5427,7 +5433,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>40</v>
@@ -5444,7 +5450,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>40</v>
@@ -5461,7 +5467,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>40</v>
@@ -5478,7 +5484,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>40</v>
@@ -5495,7 +5501,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>40</v>
@@ -5529,7 +5535,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>40</v>
@@ -5546,7 +5552,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>40</v>
@@ -5563,7 +5569,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>40</v>
@@ -5580,7 +5586,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>40</v>
@@ -5597,7 +5603,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>40</v>
@@ -5614,7 +5620,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>163</v>

--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C4A57A-57B4-4008-A375-E1593F02C062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62136B8-9982-4ABB-A3E6-EC7EF6095362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/config/units.xlsx
+++ b/config/units.xlsx
@@ -1,28 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonas\Documents\Hector\Kooperationsphase IO-Modelle\exiobase_explorer\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62136B8-9982-4ABB-A3E6-EC7EF6095362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B10E6BB-4922-428B-A46A-8FBF46A82E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exiobase" sheetId="1" r:id="rId1"/>
     <sheet name="Deutsch" sheetId="2" r:id="rId2"/>
     <sheet name="English" sheetId="4" r:id="rId3"/>
+    <sheet name="Français" sheetId="5" r:id="rId4"/>
+    <sheet name="Español" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="597">
   <si>
     <t>impact</t>
   </si>
@@ -519,9 +534,6 @@
     <t>Umweltindikator</t>
   </si>
   <si>
-    <t>Exiobase Einheit</t>
-  </si>
-  <si>
     <t>Divisor</t>
   </si>
   <si>
@@ -919,13 +931,993 @@
   </si>
   <si>
     <t>Megatonnen</t>
+  </si>
+  <si>
+    <t>Water Consumption Total</t>
+  </si>
+  <si>
+    <t>Unité EXIOBASE</t>
+  </si>
+  <si>
+    <t>Diviseur</t>
+  </si>
+  <si>
+    <t>Décimales</t>
+  </si>
+  <si>
+    <t>Nouvelle unité (FR)</t>
+  </si>
+  <si>
+    <t>Valeur ajoutée</t>
+  </si>
+  <si>
+    <r>
+      <t>Md €</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (milliards d’euros)</t>
+    </r>
+  </si>
+  <si>
+    <t>Emploi</t>
+  </si>
+  <si>
+    <t>Mio de personnes</t>
+  </si>
+  <si>
+    <t>Temps de travail</t>
+  </si>
+  <si>
+    <t>millions d’heures</t>
+  </si>
+  <si>
+    <t>Émissions de GES</t>
+  </si>
+  <si>
+    <t>kg CO₂ éq.</t>
+  </si>
+  <si>
+    <r>
+      <t>Mt CO₂-éq</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (mégatonnes)</t>
+    </r>
+  </si>
+  <si>
+    <t>Toxicité humaine</t>
+  </si>
+  <si>
+    <t>cas</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce</t>
+  </si>
+  <si>
+    <t>PAF m³·jour</t>
+  </si>
+  <si>
+    <t>EPS (dommages)</t>
+  </si>
+  <si>
+    <t>ELU</t>
+  </si>
+  <si>
+    <t>Effets cancérogènes sur la santé (H.A)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (organiques) (H.A)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (inorganiques) (H.A)</t>
+  </si>
+  <si>
+    <t>Dommages santé liés au climat (H.A)</t>
+  </si>
+  <si>
+    <t>Dommages écosystèmes dus aux substances toxiques (H.A)</t>
+  </si>
+  <si>
+    <r>
+      <t>PDF</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>m2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yr</t>
+    </r>
+  </si>
+  <si>
+    <t>PDF·m²·an</t>
+  </si>
+  <si>
+    <t>Dommages par acidification &amp; eutrophisation (H.A)</t>
+  </si>
+  <si>
+    <t>Effets cancérogènes sur la santé (E.E)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (organiques) (E.E)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (inorganiques) (E.E)</t>
+  </si>
+  <si>
+    <t>Dommages santé liés au climat (E.E)</t>
+  </si>
+  <si>
+    <t>Dommages écosystèmes dus aux substances toxiques (E.E)</t>
+  </si>
+  <si>
+    <t>Dommages par acidification &amp; eutrophisation (E.E)</t>
+  </si>
+  <si>
+    <t>Effets cancérogènes sur la santé (I.I)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (organiques) (I.I)</t>
+  </si>
+  <si>
+    <t>Maladies respiratoires (inorganiques) (I.I)</t>
+  </si>
+  <si>
+    <t>Dommages santé liés au climat (I.I)</t>
+  </si>
+  <si>
+    <t>Dommages écosystèmes dus aux substances toxiques (I.I)</t>
+  </si>
+  <si>
+    <t>Dommages par acidification &amp; eutrophisation (I.I)</t>
+  </si>
+  <si>
+    <t>Extraction de matières non utilisée</t>
+  </si>
+  <si>
+    <t>kilotonnes (kt)</t>
+  </si>
+  <si>
+    <t>Consommation d’eau verte – agriculture</t>
+  </si>
+  <si>
+    <r>
+      <t>Mm³</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (millions de m³ d’eau)</t>
+    </r>
+  </si>
+  <si>
+    <t>Consommation d’eau bleue – agriculture</t>
+  </si>
+  <si>
+    <t>Mm³</t>
+  </si>
+  <si>
+    <t>Consommation d’eau bleue – élevage</t>
+  </si>
+  <si>
+    <t>Consommation d’eau bleue – industrie</t>
+  </si>
+  <si>
+    <t>Consommation d’eau bleue – production d’électricité</t>
+  </si>
+  <si>
+    <t>Consommation d’eau bleue – ménages</t>
+  </si>
+  <si>
+    <t>Consommation d’eau (totale)</t>
+  </si>
+  <si>
+    <t>Prélèvement d’eau bleue – industrie</t>
+  </si>
+  <si>
+    <t>Prélèvement d’eau bleue – production d’électricité</t>
+  </si>
+  <si>
+    <t>Prélèvement d’eau bleue – ménages</t>
+  </si>
+  <si>
+    <t>Prélèvement d’eau bleue – total</t>
+  </si>
+  <si>
+    <t>CO₂ (IPCC cat. 1–4 &amp; 6–7, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>CH₄ (IPCC cat. 1–4 &amp; 6–7, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>N₂O (IPCC cat. 1–4 &amp; 6–7, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>CO₂-éq pour CO₂ (IPCC, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>Gg CO₂-éq</t>
+  </si>
+  <si>
+    <t>CO₂-éq pour CH₄ (IPCC, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>CO₂-éq pour N₂O (IPCC, hors UTCATF)</t>
+  </si>
+  <si>
+    <t>CO₂ – combustion &amp; ciment</t>
+  </si>
+  <si>
+    <t>CO₂ – combustion</t>
+  </si>
+  <si>
+    <t>GES (GWP100) – CML 1999 – IPCC 2007</t>
+  </si>
+  <si>
+    <t>Mt CO₂-éq</t>
+  </si>
+  <si>
+    <t>GES (GWP100min) – Houghton et al. 2001</t>
+  </si>
+  <si>
+    <t>GES (GWP100max) – Houghton et al. 2001</t>
+  </si>
+  <si>
+    <t>GES (GWP20) – IPCC 2007</t>
+  </si>
+  <si>
+    <t>GES (GWP500) – IPCC 2007</t>
+  </si>
+  <si>
+    <t>Potentiel d’appauvrissement de l’ozone (ODP, état stationnaire)</t>
+  </si>
+  <si>
+    <t>kg CFC-11 éq.</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (HTP inf) – CML</t>
+  </si>
+  <si>
+    <t>kg 1,4-DCB éq.</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce (FAETP inf) – CML</t>
+  </si>
+  <si>
+    <t>Écotoxicité marine (MAETP inf) – CML</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments eau douce (FSETP inf)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments marins (MSETP inf)</t>
+  </si>
+  <si>
+    <t>Écotoxicité terrestre (TETP inf)</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (HTP20)</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce (FAETP20)</t>
+  </si>
+  <si>
+    <t>Écotoxicité marine (MAETP20)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments eau douce (FSETP20)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments marins (MSETP20)</t>
+  </si>
+  <si>
+    <t>Écotoxicité terrestre (TETP20)</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (HTP100)</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce (FAETP100)</t>
+  </si>
+  <si>
+    <t>Écotoxicité marine (MAETP100)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments eau douce (FSETP100)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments marins (MSETP100)</t>
+  </si>
+  <si>
+    <t>Écotoxicité terrestre (TETP100)</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (HTP500)</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce (FAETP500)</t>
+  </si>
+  <si>
+    <t>Écotoxicité marine (MAETP500)</t>
+  </si>
+  <si>
+    <t>Écotoxicité sédiments eau douce (FSETP500)</t>
+  </si>
+  <si>
+    <t>Toxicité sédiments marins (MSETP500) – alternatif</t>
+  </si>
+  <si>
+    <t>Écotoxicité terrestre (TETP500) – alternatif</t>
+  </si>
+  <si>
+    <t>Oxydation photochimique (NOx élevés) – POCP</t>
+  </si>
+  <si>
+    <t>kg éthylène éq.</t>
+  </si>
+  <si>
+    <t>Oxydation photochimique (NOx faibles) – POCP</t>
+  </si>
+  <si>
+    <t>Oxydation photochimique (MIR)</t>
+  </si>
+  <si>
+    <t>kg ozone formé</t>
+  </si>
+  <si>
+    <t>Oxydation photochimique (MOIR)</t>
+  </si>
+  <si>
+    <t>Oxydation photochimique (EBIR)</t>
+  </si>
+  <si>
+    <t>Acidification (avec “sort”/fate)</t>
+  </si>
+  <si>
+    <t>kg SO₂ éq.</t>
+  </si>
+  <si>
+    <t>Acidification (sans “sort”/fate)</t>
+  </si>
+  <si>
+    <t>Eutrophisation (sans “sort”/fate)</t>
+  </si>
+  <si>
+    <t>kg PO₄³⁻ éq.</t>
+  </si>
+  <si>
+    <t>Eutrophisation (avec “sort”/fate)</t>
+  </si>
+  <si>
+    <t>kg NOx éq.</t>
+  </si>
+  <si>
+    <t>Odeur</t>
+  </si>
+  <si>
+    <t>Changement climatique (moyenne, ILCD) – GWP100</t>
+  </si>
+  <si>
+    <t>kg CO₂-éq</t>
+  </si>
+  <si>
+    <t>CC – endpoint santé humaine (ILCD)</t>
+  </si>
+  <si>
+    <t>CC – endpoint écosystèmes (ILCD)</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (cancer, ILCD)</t>
+  </si>
+  <si>
+    <t>CTUh/kg</t>
+  </si>
+  <si>
+    <t>Toxicité humaine (non-cancer, ILCD)</t>
+  </si>
+  <si>
+    <t>CTUh</t>
+  </si>
+  <si>
+    <t>Toxicité humaine endpoint (cancer, ILCD)</t>
+  </si>
+  <si>
+    <t>Toxicité humaine endpoint (non-cancer, ILCD)</t>
+  </si>
+  <si>
+    <t>Particules fines / inorganiques resp. (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>kg PM2.5-éq</t>
+  </si>
+  <si>
+    <t>Particules fines endpoint (ILCD)</t>
+  </si>
+  <si>
+    <t>Ozone photochimique (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>kg C₂H₄-éq</t>
+  </si>
+  <si>
+    <t>Ozone photochimique endpoint (ILCD)</t>
+  </si>
+  <si>
+    <t>Acidification (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>Acidification endpoint (ILCD)</t>
+  </si>
+  <si>
+    <t>Eutrophisation terrestre (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>Eutrophisation marine (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>kg N-éq</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce (midpoint, ILCD)</t>
+  </si>
+  <si>
+    <t>CTUe (PAF·m³·an)</t>
+  </si>
+  <si>
+    <t>Écotoxicité eau douce endpoint (ILCD)</t>
+  </si>
+  <si>
+    <t>PDF·m³·an</t>
+  </si>
+  <si>
+    <t>GES AR5 (GWP100) – IPCC 2010</t>
+  </si>
+  <si>
+    <t>Azote</t>
+  </si>
+  <si>
+    <r>
+      <t>Mt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (mégatonnes)</t>
+    </r>
+  </si>
+  <si>
+    <t>Phosphore</t>
+  </si>
+  <si>
+    <t>Mt</t>
+  </si>
+  <si>
+    <t>PM2.5</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – récoltes &amp; résidus</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – pâturages &amp; fourrages</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – foresterie &amp; bois</t>
+  </si>
+  <si>
+    <t>Extraction domestique utilisée – pêches</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – minéraux non métalliques</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – minerai de fer</t>
+  </si>
+  <si>
+    <t>Utilisation de l’extraction domestique – minerais non ferreux</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – récoltes &amp; résidus</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – pâturages &amp; fourrages</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – foresterie &amp; bois</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – pêches</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – charbon &amp; tourbe</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – pétrole &amp; gaz</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – minéraux non métalliques</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – minerai de fer</t>
+  </si>
+  <si>
+    <t>Extraction domestique non utilisée – minerais non ferreux</t>
+  </si>
+  <si>
+    <t>Occupation des sols</t>
+  </si>
+  <si>
+    <r>
+      <t>Mha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (millions d’hectares)</t>
+    </r>
+  </si>
+  <si>
+    <t>Indicateur environnemental</t>
+  </si>
+  <si>
+    <t>EXIOBASE Einheit</t>
+  </si>
+  <si>
+    <t>Unidad EXIOBASE</t>
+  </si>
+  <si>
+    <t>Decimales</t>
+  </si>
+  <si>
+    <t>Valor añadido</t>
+  </si>
+  <si>
+    <t>Empleo</t>
+  </si>
+  <si>
+    <t>millones de personas</t>
+  </si>
+  <si>
+    <t>Tiempo de trabajo</t>
+  </si>
+  <si>
+    <t>millones de horas</t>
+  </si>
+  <si>
+    <t>Toxicidad humana</t>
+  </si>
+  <si>
+    <t>casos</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce</t>
+  </si>
+  <si>
+    <t>Efectos cancerígenos en humanos (H.A)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias orgánicas (H.A)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias inorgánicas (H.A)</t>
+  </si>
+  <si>
+    <t>Daños a la salud por cambio climático (H.A)</t>
+  </si>
+  <si>
+    <t>Daños por acidificación y eutrofización (H.A)</t>
+  </si>
+  <si>
+    <t>Efectos cancerígenos en humanos (E.E)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias orgánicas (E.E)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias inorgánicas (E.E)</t>
+  </si>
+  <si>
+    <t>Daños a la salud por cambio climático (E.E)</t>
+  </si>
+  <si>
+    <t>Daños por acidificación y eutrofización (E.E)</t>
+  </si>
+  <si>
+    <t>Efectos cancerígenos en humanos (I.I)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias orgánicas (I.I)</t>
+  </si>
+  <si>
+    <t>Enfermedades respiratorias por sustancias inorgánicas (I.I)</t>
+  </si>
+  <si>
+    <t>Daños a la salud por cambio climático (I.I)</t>
+  </si>
+  <si>
+    <t>Daños por acidificación y eutrofización (I.I)</t>
+  </si>
+  <si>
+    <t>Extracción de recursos no utilizada</t>
+  </si>
+  <si>
+    <t>Nitrógeno</t>
+  </si>
+  <si>
+    <t>Fósforo</t>
+  </si>
+  <si>
+    <t>Uso del suelo</t>
+  </si>
+  <si>
+    <t>kilotoneladas</t>
+  </si>
+  <si>
+    <t>Consumo de agua verde - agricultura</t>
+  </si>
+  <si>
+    <t>millones de m³ de agua</t>
+  </si>
+  <si>
+    <t>Consumo de agua azul - agricultura</t>
+  </si>
+  <si>
+    <t>Consumo de agua azul - ganadería</t>
+  </si>
+  <si>
+    <t>Consumo de agua azul - industria</t>
+  </si>
+  <si>
+    <t>Consumo de agua azul - generación eléctrica</t>
+  </si>
+  <si>
+    <t>Consumo de agua azul - hogares</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (HTP inf) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (FAETP inf) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad terrestre (TETP inf) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (HTP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (FAETP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad terrestre (TETP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (HTP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (FAETP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad terrestre (TETP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (HTP500) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Indicador ambiental</t>
+  </si>
+  <si>
+    <t>Nueva unidad</t>
+  </si>
+  <si>
+    <t>miles de millones de euros</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero</t>
+  </si>
+  <si>
+    <t>megatoneladas de CO2-eq</t>
+  </si>
+  <si>
+    <t>Enfoque de daños EPS</t>
+  </si>
+  <si>
+    <t>Daños a la calidad de los ecosistemas por sustancias nocivas (H.A)</t>
+  </si>
+  <si>
+    <t>Daños a la calidad de los ecosistemas por sustancias nocivas (E.E)</t>
+  </si>
+  <si>
+    <t>Daños a la calidad de los ecosistemas por sustancias nocivas (I.I)</t>
+  </si>
+  <si>
+    <t>Consumo de agua</t>
+  </si>
+  <si>
+    <t>Extracción de agua azul - industria</t>
+  </si>
+  <si>
+    <t>Extracción de agua azul - generación eléctrica</t>
+  </si>
+  <si>
+    <t>Extracción de agua azul - hogares</t>
+  </si>
+  <si>
+    <t>Extracción de agua azul - total</t>
+  </si>
+  <si>
+    <t>Dióxido de carbono (CO₂) IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo y silvicultura)</t>
+  </si>
+  <si>
+    <t>Metano (CH₄) IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo y silvicultura)</t>
+  </si>
+  <si>
+    <t>Óxido nitroso (N₂O) IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo y silvicultura)</t>
+  </si>
+  <si>
+    <t>CO₂-equivalente (CO₂eq) para CO₂ IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo)</t>
+  </si>
+  <si>
+    <t>CO₂-equivalente (CO₂eq) para metano (CH₄) IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo)</t>
+  </si>
+  <si>
+    <t>CO₂-equivalente (CO₂eq) para óxido nitroso (N₂O) IPCC categorías 1-4 y 6-7 (sin uso/cambio de uso del suelo)</t>
+  </si>
+  <si>
+    <t>Dióxido de carbono (CO₂) procedente de la combustión de combustibles y la producción de cemento</t>
+  </si>
+  <si>
+    <t>Dióxido de carbono (CO₂) procedente de la combustión de combustibles</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero (GWP100) | Enfoque base (CML, 1999) | GWP100 (IPCC, 2007)</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero (GWP100min) | Enfoque alternativo | GWP100 neto mín. (Houghton et al., 2001)</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero (GWP100max) | Enfoque alternativo | GWP100 neto máx. (Houghton et al., 2001)</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero (GWP20) | Enfoque alternativo | GWP20 (IPCC, 2007)</t>
+  </si>
+  <si>
+    <t>Emisiones de gases de efecto invernadero (GWP500) | Enfoque alternativo | GWP500 (IPCC, 2007)</t>
+  </si>
+  <si>
+    <t>Potencial de agotamiento del ozono (ODP, estado estacionario) | Enfoque orientado al problema: base | ODP, estado estacionario</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en el medio marino (MAETP inf) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en agua dulce (FSETP inf) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en el medio marino (MSETP inf) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en el medio marino (MAETP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en agua dulce (FSETP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en el medio marino (MSETP20) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en el medio marino (MAETP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en agua dulce (FSETP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en el medio marino (MSETP100) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (FAETP500) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en el medio marino (MAETP500) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad sedimentaria en agua dulce (FSETP500) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Toxicidad de sedimentos marinos (MSETP500) | Enfoque alternativo (CML, 1999) | MSETP 500 (Huijbregts, 1999 y 2000)</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad terrestre (TETP500) | Enfoque alternativo (CML, 1999) | TETP 500 (Huijbregts, 1999 y 2000)</t>
+  </si>
+  <si>
+    <t>Oxidación fotoquímica (valores altos de NOx) | Enfoque base (CML, 1999) | POCP (Jenkin y Hayman, 1999; Derwent et al., 1998)</t>
+  </si>
+  <si>
+    <t>Oxidación fotoquímica (valores bajos de NOx) | Enfoque alternativo (CML, 1999) | POCP (Andersson-Sköld et al., 1992)</t>
+  </si>
+  <si>
+    <t>Oxidación fotoquímica (MIR; valores muy altos de NOx) | Enfoque alternativo (CML, 1999) | MIR 1997 (Carter, 1994, 1997, 1998; Carter et al., 1995)</t>
+  </si>
+  <si>
+    <t>Oxidación fotoquímica (MOIR; NOx alto) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Oxidación fotoquímica (EBIR; NOx bajo) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Acidificación (incl. destino, media Europa total, A&amp;B) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Acidificación (sin destino) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Eutrofización (sin destino) | Enfoque orientado al problema: base</t>
+  </si>
+  <si>
+    <t>Eutrofización (incl. destino, media Europa total, A&amp;B) | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Olor | Enfoque orientado al problema: no base</t>
+  </si>
+  <si>
+    <t>Cambio climático (promedio) | CF recomendado por ILCD | Potencial de calentamiento global a 100 años</t>
+  </si>
+  <si>
+    <t>Cambio climático (endpoint), salud humana | CF recomendado por ILCD | Años de vida ajustados por discapacidad (DALY)</t>
+  </si>
+  <si>
+    <t>Cambio climático (endpoint), ecosistemas | CF recomendado por ILCD | Fracción de especies potencialmente desaparecidas (PDF)</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (promedio), efectos cancerígenos | CF recomendado por ILCD | Unidad comparativa para toxicidad humana (CTUh)</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (promedio), sin efectos cancerígenos | CF recomendado por ILCD | Unidad comparativa para toxicidad humana (CTUh)</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (endpoint), efectos cancerígenos | CF recomendado por ILCD | Años de vida ajustados por discapacidad (DALY)</t>
+  </si>
+  <si>
+    <t>Toxicidad humana (endpoint), sin efectos cancerígenos | CF recomendado por ILCD | Años de vida ajustados por discapacidad (DALY)</t>
+  </si>
+  <si>
+    <t>Partículas finas / sustancias inorgánicas respiratorias (promedio) | CF recomendado por ILCD | Equivalente medio ponderado por emisiones de PM2,5</t>
+  </si>
+  <si>
+    <t>Partículas finas / sustancias inorgánicas respiratorias (endpoint) | CF recomendado por ILCD | Años de vida ajustados por discapacidad (DALY)</t>
+  </si>
+  <si>
+    <t>Formación de ozono fotoquímico (promedio), salud humana | CF recomendado por ILCD | Potencial de formación de ozono fotoquímico (POCP)</t>
+  </si>
+  <si>
+    <t>Formación de ozono fotoquímico (endpoint), salud humana | CF recomendado por ILCD | Años de vida ajustados por discapacidad (DALY)</t>
+  </si>
+  <si>
+    <t>Acidificación (promedio) | CF recomendado por ILCD | Excedencia acumulada (AE)</t>
+  </si>
+  <si>
+    <t>Acidificación (endpoint) | CF recomendado por ILCD | Cambio en la fracción de especies vegetales potencialmente ausentes por cambio en la saturación de bases</t>
+  </si>
+  <si>
+    <t>Eutrofización terrestre (promedio) | CF recomendado por ILCD | Excedencia acumulada (AE)</t>
+  </si>
+  <si>
+    <t>Eutrofización marina (promedio) | CF recomendado por ILCD | Fracciones de especies potencialmente desaparecidas (PDF)</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (promedio) | CF recomendado por ILCD | Unidad comparativa para ecosistemas (CTUe)</t>
+  </si>
+  <si>
+    <t>Ecotoxicidad en agua dulce (endpoint) | CF recomendado por ILCD | Fracciones de especies potencialmente desaparecidas (PDF)</t>
+  </si>
+  <si>
+    <t>Emisiones de GEI AR5 (GWP100) | GWP100 (IPCC, 2010)</t>
+  </si>
+  <si>
+    <t>megatoneladas</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - cosecha y residuos de cosecha</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - pastos y forraje</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - silvicultura y madera</t>
+  </si>
+  <si>
+    <t>Extracción doméstica utilizada – pesca</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - minerales no metálicos</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - mineral de hierro</t>
+  </si>
+  <si>
+    <t>Uso de la extracción doméstica - minerales de metales no ferrosos</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - cosecha y residuos de cosecha</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - pastos y forraje</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - silvicultura y madera</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada – pesca</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - carbón y turba</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - petróleo y gas</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - minerales no metálicos</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - mineral de hierro</t>
+  </si>
+  <si>
+    <t>Extracción doméstica no utilizada - minerales de metales no ferrosos</t>
+  </si>
+  <si>
+    <t>millones de hectáreas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,6 +1931,14 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3481,21 +4481,21 @@
         <v>164</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -3507,12 +4507,12 @@
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -3524,12 +4524,12 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
@@ -3541,12 +4541,12 @@
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -3558,12 +4558,12 @@
         <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
@@ -3575,12 +4575,12 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -3597,7 +4597,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -3614,7 +4614,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>20</v>
@@ -3631,7 +4631,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -3648,7 +4648,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
@@ -3665,7 +4665,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
@@ -3682,7 +4682,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
@@ -3699,7 +4699,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
@@ -3716,7 +4716,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
@@ -3733,7 +4733,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
@@ -3750,7 +4750,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>20</v>
@@ -3767,7 +4767,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>20</v>
@@ -3784,7 +4784,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>25</v>
@@ -3801,7 +4801,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>25</v>
@@ -3818,7 +4818,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>20</v>
@@ -3835,7 +4835,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
@@ -3852,7 +4852,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>20</v>
@@ -3869,7 +4869,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>20</v>
@@ -3886,7 +4886,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>25</v>
@@ -3903,7 +4903,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>25</v>
@@ -3920,7 +4920,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>40</v>
@@ -3932,12 +4932,12 @@
         <v>2</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>42</v>
@@ -3949,12 +4949,12 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
@@ -3966,12 +4966,12 @@
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
@@ -3983,12 +4983,12 @@
         <v>2</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
@@ -4000,12 +5000,12 @@
         <v>2</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
@@ -4017,12 +5017,12 @@
         <v>2</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>42</v>
@@ -4034,12 +5034,12 @@
         <v>2</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
@@ -4051,12 +5051,12 @@
         <v>2</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>42</v>
@@ -4068,12 +5068,12 @@
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>42</v>
@@ -4085,12 +5085,12 @@
         <v>2</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>42</v>
@@ -4102,12 +5102,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>42</v>
@@ -4119,12 +5119,12 @@
         <v>2</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>54</v>
@@ -4141,7 +5141,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>54</v>
@@ -4158,7 +5158,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>54</v>
@@ -4175,7 +5175,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>58</v>
@@ -4192,7 +5192,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>58</v>
@@ -4209,7 +5209,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>58</v>
@@ -4226,7 +5226,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>54</v>
@@ -4243,7 +5243,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>54</v>
@@ -4260,7 +5260,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
@@ -4272,12 +5272,12 @@
         <v>2</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
@@ -4289,12 +5289,12 @@
         <v>2</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
@@ -4306,12 +5306,12 @@
         <v>2</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
@@ -4323,12 +5323,12 @@
         <v>2</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
@@ -4340,12 +5340,12 @@
         <v>2</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>69</v>
@@ -4362,7 +5362,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>71</v>
@@ -4379,7 +5379,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>71</v>
@@ -4396,7 +5396,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>71</v>
@@ -4413,7 +5413,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>71</v>
@@ -4430,7 +5430,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>71</v>
@@ -4447,7 +5447,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>71</v>
@@ -4464,7 +5464,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>71</v>
@@ -4481,7 +5481,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>71</v>
@@ -4498,7 +5498,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>71</v>
@@ -4515,7 +5515,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>71</v>
@@ -4532,7 +5532,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>71</v>
@@ -4549,7 +5549,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>71</v>
@@ -4566,7 +5566,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>71</v>
@@ -4583,7 +5583,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>71</v>
@@ -4600,7 +5600,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>71</v>
@@ -4617,7 +5617,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>71</v>
@@ -4634,7 +5634,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>71</v>
@@ -4651,7 +5651,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>71</v>
@@ -4668,7 +5668,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>71</v>
@@ -4685,7 +5685,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>71</v>
@@ -4702,7 +5702,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>71</v>
@@ -4719,7 +5719,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>71</v>
@@ -4736,7 +5736,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>71</v>
@@ -4753,7 +5753,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>71</v>
@@ -4770,7 +5770,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>96</v>
@@ -4787,7 +5787,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>96</v>
@@ -4804,7 +5804,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>99</v>
@@ -4821,7 +5821,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>99</v>
@@ -4838,7 +5838,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -4855,7 +5855,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>103</v>
@@ -4872,7 +5872,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -4889,7 +5889,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>106</v>
@@ -4906,7 +5906,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>108</v>
@@ -4923,7 +5923,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>110</v>
@@ -4935,12 +5935,12 @@
         <v>2</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>112</v>
@@ -4957,7 +5957,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>20</v>
@@ -4974,7 +5974,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
@@ -4991,7 +5991,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
@@ -5008,7 +6008,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
@@ -5025,7 +6025,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>20</v>
@@ -5042,7 +6042,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>20</v>
@@ -5059,7 +6059,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>123</v>
@@ -5076,7 +6076,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>20</v>
@@ -5093,7 +6093,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>126</v>
@@ -5110,7 +6110,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>20</v>
@@ -5127,7 +6127,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>129</v>
@@ -5144,7 +6144,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>115</v>
@@ -5161,7 +6161,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>129</v>
@@ -5178,7 +6178,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>133</v>
@@ -5195,7 +6195,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>135</v>
@@ -5212,7 +6212,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>137</v>
@@ -5229,7 +6229,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>12</v>
@@ -5241,12 +6241,12 @@
         <v>2</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>140</v>
@@ -5258,12 +6258,12 @@
         <v>2</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>140</v>
@@ -5275,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -5292,7 +6292,7 @@
         <v>2</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -5309,7 +6309,7 @@
         <v>2</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,7 +6326,7 @@
         <v>2</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -5343,12 +6343,12 @@
         <v>2</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>40</v>
@@ -5365,7 +6365,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>40</v>
@@ -5382,7 +6382,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>40</v>
@@ -5416,7 +6416,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>40</v>
@@ -5433,7 +6433,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>40</v>
@@ -5450,7 +6450,7 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>40</v>
@@ -5467,7 +6467,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>40</v>
@@ -5484,7 +6484,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>40</v>
@@ -5501,7 +6501,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>40</v>
@@ -5535,7 +6535,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>40</v>
@@ -5552,7 +6552,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>40</v>
@@ -5569,7 +6569,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>40</v>
@@ -5586,7 +6586,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>40</v>
@@ -5603,7 +6603,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>40</v>
@@ -5620,7 +6620,7 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>163</v>
@@ -5632,7 +6632,7 @@
         <v>2</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -6216,7 +7216,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>48</v>
+        <v>298</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>42</v>
@@ -7815,4 +8815,4356 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CD7811-AFAA-4433-8965-1D8E59BE522F}">
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <v>2</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>2</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>2</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>2</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2">
+        <v>2</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2">
+        <v>2</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D104" s="2">
+        <v>2</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D105" s="2">
+        <v>2</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D109" s="2">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D110" s="2">
+        <v>2</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2">
+        <v>2</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2">
+        <v>2</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2">
+        <v>2</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>2</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2">
+        <v>2</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
+        <v>2</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>2</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
+        <v>2</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>2</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>2</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>2</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
+        <v>2</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>2</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
+        <v>2</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>2</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>2</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D127" s="2">
+        <v>2</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811DC47B-AF46-4208-A090-411783CB4C6D}">
+  <dimension ref="A1:E127"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="146.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>2</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>2</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>2</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>2</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>2</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D47" s="2">
+        <v>2</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D49" s="2">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <v>2</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2">
+        <v>2</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>2</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <v>2</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <v>2</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>2</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>2</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <v>2</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>2</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C74" s="2">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
+        <v>2</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C85" s="2">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
+        <v>2</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86" s="2">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
+        <v>2</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87" s="2">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <v>2</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="2">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>2</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C89" s="2">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="2">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2">
+        <v>2</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="2">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C92" s="2">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2">
+        <v>2</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="2">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>2</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C94" s="2">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
+        <v>2</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="2">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>2</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C96" s="2">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2">
+        <v>2</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" s="2">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2">
+        <v>2</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C98" s="2">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2">
+        <v>2</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C99" s="2">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C100" s="2">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
+        <v>2</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" s="2">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C103" s="2">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2">
+        <v>2</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D104" s="2">
+        <v>2</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D105" s="2">
+        <v>2</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D109" s="2">
+        <v>2</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="D110" s="2">
+        <v>2</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" s="2">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2">
+        <v>2</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" s="2">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2">
+        <v>2</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C113" s="2">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2">
+        <v>2</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>2</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2">
+        <v>2</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116" s="2">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2">
+        <v>2</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>2</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
+        <v>2</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>2</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>2</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>2</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2">
+        <v>2</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>2</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C124" s="2">
+        <v>1</v>
+      </c>
+      <c r="D124" s="2">
+        <v>2</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2">
+        <v>2</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>2</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C127" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D127" s="2">
+        <v>2</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>